--- a/results/job_matches_2026-08-23.xlsx
+++ b/results/job_matches_2026-08-23.xlsx
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Claritas Rx</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.9</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, Hadoop, Hive, Sqoop, MapReduce, YARN</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, SQS, ECS, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48397f4e7a2d566c</t>
+          <t>https://www.indeed.com/viewjob?jk=e12b8c592b8fca76</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Solutions Delivery Engineer (Remote)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Claritas Rx</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>12.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, SQS, ECS, IAM, RDS, Spark</t>
+          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e12b8c592b8fca76</t>
+          <t>https://www.indeed.com/viewjob?jk=ec761fb42adb289d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Solutions Delivery Engineer (Remote)</t>
+          <t>Senior Software Development Engineer - LLMs, GenAI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,34 +556,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec761fb42adb289d</t>
+          <t>https://www.indeed.com/viewjob?jk=7ef55c2266d41678</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Senior Professional Services Consultant</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef55c2266d41678</t>
+          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Professional Services Consultant</t>
+          <t>Delivery Senior Consultant, Data Engineering and Conversion Solutions</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>Redshift, Azure, Databricks, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, Talend, dbt</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6f3843c2e2f33e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-23.xlsx
+++ b/results/job_matches_2026-08-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,41 +672,6 @@
       <c r="G7" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8d51d47e65997196</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33b30501746ad4bf</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-23.xlsx
+++ b/results/job_matches_2026-08-23.xlsx
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Professional Services Consultant</t>
+          <t>Delivery Senior Consultant, Data Engineering and Conversion Solutions</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Kafka, Snowflake</t>
+          <t>Redshift, Azure, Databricks, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, Talend, dbt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f49a3f3dbcbca27</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6f3843c2e2f33e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Delivery Senior Consultant, Data Engineering and Conversion Solutions</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Youth Villages</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, Talend, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6f3843c2e2f33e</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d419dc292622cd</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-23.xlsx
+++ b/results/job_matches_2026-08-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Solutions Delivery Engineer (Remote)</t>
+          <t>Delivery Senior Consultant, Data Engineering and Conversion Solutions</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT</t>
+          <t>Redshift, Azure, Databricks, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, Talend, dbt</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec761fb42adb289d</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6f3843c2e2f33e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - LLMs, GenAI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Youth Villages</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Power BI, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,110 +566,40 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ef55c2266d41678</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d419dc292622cd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Delivery Senior Consultant, Data Engineering and Conversion Solutions</t>
+          <t>Site Reliability Engineering (SRE) - Maryland, US</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, Talend, dbt</t>
+          <t>Azure, GCP, BigQuery, Zookeeper, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6f3843c2e2f33e</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Youth Villages</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Chesterfield, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d419dc292622cd</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineering (SRE) - Maryland, US</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Azure, GCP, BigQuery, Zookeeper, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8d51d47e65997196</t>
         </is>

--- a/results/job_matches_2026-08-23.xlsx
+++ b/results/job_matches_2026-08-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,41 +567,6 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f3d419dc292622cd</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineering (SRE) - Maryland, US</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Azure, GCP, BigQuery, Zookeeper, Scala, Kafka, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d51d47e65997196</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-23.xlsx
+++ b/results/job_matches_2026-08-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,12 +503,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Delivery Senior Consultant, Data Engineering and Conversion Solutions</t>
+          <t>Senior Machine Learning Engineer (MLOPS)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,54 +517,89 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, Talend, dbt</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6f3843c2e2f33e</t>
+          <t>https://www.indeed.com/viewjob?jk=fdb054133d54c854</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Delivery Senior Consultant, Data Engineering and Conversion Solutions</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Redshift, Azure, Databricks, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, Talend, dbt</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f6f3843c2e2f33e</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Data Engineer</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Youth Villages</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Chesterfield, VA, US USA</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>10.4</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f3d419dc292622cd</t>
         </is>

--- a/results/job_matches_2026-08-23.xlsx
+++ b/results/job_matches_2026-08-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,47 +468,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Senior Machine Learning Engineer (MLOPS)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Claritas Rx</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.4</v>
+        <v>13.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, SQS, ECS, IAM, RDS, Spark</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e12b8c592b8fca76</t>
+          <t>https://www.indeed.com/viewjob?jk=fdb054133d54c854</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (MLOPS)</t>
+          <t>Delivery Senior Consultant, Data Engineering and Conversion Solutions</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,46 +517,46 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>Redshift, Azure, Databricks, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, Talend, dbt</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdb054133d54c854</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6f3843c2e2f33e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Delivery Senior Consultant, Data Engineering and Conversion Solutions</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Youth Villages</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, Talend, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -565,41 +565,6 @@
         </is>
       </c>
       <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6f3843c2e2f33e</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Youth Villages</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Chesterfield, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f3d419dc292622cd</t>
         </is>

--- a/results/job_matches_2026-08-23.xlsx
+++ b/results/job_matches_2026-08-23.xlsx
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Delivery Senior Consultant, Data Engineering and Conversion Solutions</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, Talend, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6f3843c2e2f33e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e3fcc35e91c6408</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Delivery Senior Consultant, Data Engineering and Conversion Solutions</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Youth Villages</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chesterfield, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
+          <t>Redshift, Azure, Databricks, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, Talend, dbt</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d419dc292622cd</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6f3843c2e2f33e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-23.xlsx
+++ b/results/job_matches_2026-08-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (MLOPS)</t>
+          <t>Onsite_CCaaS - Five9 GCP Data Engineer_ Sunrise, FL || Charlotte, NC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, Hive, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdb054133d54c854</t>
+          <t>https://www.indeed.com/viewjob?jk=93687bce41c54bba</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Senior Machine Learning Engineer (MLOPS)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,40 +531,75 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e3fcc35e91c6408</t>
+          <t>https://www.indeed.com/viewjob?jk=fdb054133d54c854</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Software Engineer III - AI/ML Developer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e3fcc35e91c6408</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Delivery Senior Consultant, Data Engineering and Conversion Solutions</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Deloitte</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Atlanta, GA, US USA</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>11.8</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Redshift, Azure, Databricks, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, Talend, dbt</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7f6f3843c2e2f33e</t>
         </is>
